--- a/data/Wohlen (AG)/investment_decision/Wohlen AG_MFH_until_2004_investment_decision.xlsx
+++ b/data/Wohlen (AG)/investment_decision/Wohlen AG_MFH_until_2004_investment_decision.xlsx
@@ -461,32 +461,32 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>565.9051157216115</v>
+        <v>722.0117987643524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>1159520.506392331</v>
       </c>
       <c r="F2" t="n">
-        <v>565.9051157216115</v>
+        <v>742.8223014378218</v>
       </c>
       <c r="G2" t="n">
         <v>1159520.506392331</v>
       </c>
       <c r="H2" t="n">
-        <v>569.4097419156872</v>
+        <v>683.3317114679143</v>
       </c>
       <c r="I2" t="n">
         <v>1159520.506392331</v>
       </c>
       <c r="J2" t="n">
-        <v>565.9051157216115</v>
+        <v>743.8023159298525</v>
       </c>
       <c r="K2" t="n">
         <v>1159520.506392331</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>1720.600357107693</v>
+        <v>1002.092478251755</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>1159520.506392331</v>
       </c>
       <c r="F3" t="n">
-        <v>1708.276297635162</v>
+        <v>1002.092478251755</v>
       </c>
       <c r="G3" t="n">
         <v>1159520.506392331</v>
       </c>
       <c r="H3" t="n">
-        <v>1766.628140776557</v>
+        <v>1002.092478251756</v>
       </c>
       <c r="I3" t="n">
         <v>1159520.506392331</v>
       </c>
       <c r="J3" t="n">
-        <v>1739.13711389597</v>
+        <v>1002.092478251756</v>
       </c>
       <c r="K3" t="n">
         <v>1159520.506392331</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>3191.150902148473</v>
+        <v>2613.547879116917</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>1159520.506392331</v>
       </c>
       <c r="F4" t="n">
-        <v>3177.22703754447</v>
+        <v>2614.898312723405</v>
       </c>
       <c r="G4" t="n">
         <v>1159520.506392331</v>
       </c>
       <c r="H4" t="n">
-        <v>3186.598398637192</v>
+        <v>2584.106214966774</v>
       </c>
       <c r="I4" t="n">
         <v>1159520.506392331</v>
       </c>
       <c r="J4" t="n">
-        <v>3234.960157403665</v>
+        <v>2591.875060542968</v>
       </c>
       <c r="K4" t="n">
         <v>1159520.506392331</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>3626.2766922171</v>
+        <v>4116.684799995796</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>1159520.506392331</v>
       </c>
       <c r="F5" t="n">
-        <v>3639.645014180221</v>
+        <v>4116.37538313031</v>
       </c>
       <c r="G5" t="n">
         <v>1159520.506392331</v>
       </c>
       <c r="H5" t="n">
-        <v>3639.645014180221</v>
+        <v>4116.684799995794</v>
       </c>
       <c r="I5" t="n">
         <v>1159520.506392331</v>
       </c>
       <c r="J5" t="n">
-        <v>3668.056259859676</v>
+        <v>4116.375383130312</v>
       </c>
       <c r="K5" t="n">
         <v>1159520.506392331</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>3626.2766922171</v>
+        <v>4116.684799995796</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>1159520.506392331</v>
       </c>
       <c r="F6" t="n">
-        <v>3639.645014180221</v>
+        <v>4116.37538313031</v>
       </c>
       <c r="G6" t="n">
         <v>1159520.506392331</v>
       </c>
       <c r="H6" t="n">
-        <v>3639.645014180221</v>
+        <v>4116.684799995794</v>
       </c>
       <c r="I6" t="n">
         <v>1159520.506392331</v>
       </c>
       <c r="J6" t="n">
-        <v>3668.056259859676</v>
+        <v>4116.375383130312</v>
       </c>
       <c r="K6" t="n">
         <v>1159520.506392331</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Wohlen AG_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Wohlen AG_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>1739.280759588497</v>
+        <v>2207.125028089888</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1739.280759588497</v>
+        <v>1062.792227739638</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>837.5121706392368</v>
+        <v>1062.792227739638</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>837.5121706392368</v>
+        <v>2207.125028089888</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Wohlen AG_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Wohlen AG_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>1739.280759588497</v>
+        <v>2207.125028089888</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1739.280759588497</v>
+        <v>1513.723981529316</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1192.859925420776</v>
+        <v>1513.723981529316</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1192.859925420776</v>
+        <v>2207.125028089888</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Wohlen AG_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Wohlen AG_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>1739.280759588497</v>
+        <v>2207.125028089888</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1739.280759588497</v>
+        <v>1740.67481483007</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1371.703993024046</v>
+        <v>1740.67481483007</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1371.703993024046</v>
+        <v>2207.125028089888</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Wohlen AG_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Wohlen AG_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>1739.280759588497</v>
+        <v>2207.125028089888</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1739.280759588497</v>
+        <v>1869.172356756704</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1472.963912368457</v>
+        <v>1869.172356756704</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1472.963912368457</v>
+        <v>2207.125028089888</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Wohlen AG_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Wohlen AG_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>1739.280759588497</v>
+        <v>2207.125028089888</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1739.280759588497</v>
+        <v>1948.481052850894</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1535.461545003275</v>
+        <v>1948.481052850894</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1535.461545003275</v>
+        <v>2207.125028089888</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3685258297882353</v>
+        <v>0.3044343811294118</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3685258297882353</v>
+        <v>0.3044343811294118</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3685258297882353</v>
+        <v>0.3044343811294118</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3685258297882353</v>
+        <v>0.3044343811294118</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3685258297882353</v>
+        <v>0.3044343811294118</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3685258297882353</v>
+        <v>0.3044343811294118</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3685258297882353</v>
+        <v>0.3044343811294118</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3685258297882353</v>
+        <v>0.3044343811294118</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3774193342264268</v>
+        <v>0.3364801054588235</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3766960238808227</v>
+        <v>0.335898998436331</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3771828429230598</v>
+        <v>0.3364801054588235</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3801582457057244</v>
+        <v>0.3364801054588235</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3875495003643717</v>
+        <v>0.337367218349557</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3882826226112687</v>
+        <v>0.3373672183495569</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3884602099304991</v>
+        <v>0.3373672183495569</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3904463245224733</v>
+        <v>0.337367218349557</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3942331687764281</v>
+        <v>0.337367218349557</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3949952631255478</v>
+        <v>0.3373672183495569</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3937122061653081</v>
+        <v>0.3373672183495569</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3966149166500141</v>
+        <v>0.337367218349557</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.07633015215663974</v>
+        <v>1.683074628563601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
         <v>57.201617928</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2310761151098906</v>
+        <v>1.520883487116458</v>
       </c>
       <c r="G17" t="n">
         <v>57.201617928</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1982202445404324</v>
+        <v>2.075418511779773</v>
       </c>
       <c r="I17" t="n">
         <v>57.201617928</v>
       </c>
       <c r="J17" t="n">
-        <v>0.09310837427956531</v>
+        <v>1.469397747798732</v>
       </c>
       <c r="K17" t="n">
         <v>57.201617928</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>1.81066643711538</v>
+        <v>10.13366486172667</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>57.201617928</v>
       </c>
       <c r="F18" t="n">
-        <v>1.926204494670355</v>
+        <v>10.13366486172666</v>
       </c>
       <c r="G18" t="n">
         <v>57.201617928</v>
       </c>
       <c r="H18" t="n">
-        <v>1.561731165890088</v>
+        <v>10.13366486172665</v>
       </c>
       <c r="I18" t="n">
         <v>57.201617928</v>
       </c>
       <c r="J18" t="n">
-        <v>1.689079678916516</v>
+        <v>10.13366486172666</v>
       </c>
       <c r="K18" t="n">
         <v>57.201617928</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>4.864781573442147</v>
+        <v>15.25250484025859</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>57.201617928</v>
       </c>
       <c r="F19" t="n">
-        <v>4.941633297662588</v>
+        <v>14.62498587051192</v>
       </c>
       <c r="G19" t="n">
         <v>57.201617928</v>
       </c>
       <c r="H19" t="n">
-        <v>4.889908774424899</v>
+        <v>14.86028401970879</v>
       </c>
       <c r="I19" t="n">
         <v>57.201617928</v>
       </c>
       <c r="J19" t="n">
-        <v>4.573772228766781</v>
+        <v>14.94326365066826</v>
       </c>
       <c r="K19" t="n">
         <v>57.201617928</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>4.788451421285507</v>
+        <v>13.56943021169499</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>57.201617928</v>
       </c>
       <c r="F20" t="n">
-        <v>4.710557182552698</v>
+        <v>13.10410238339546</v>
       </c>
       <c r="G20" t="n">
         <v>57.201617928</v>
       </c>
       <c r="H20" t="n">
-        <v>4.691688529884467</v>
+        <v>12.78486550792901</v>
       </c>
       <c r="I20" t="n">
         <v>57.201617928</v>
       </c>
       <c r="J20" t="n">
-        <v>4.480663854487215</v>
+        <v>13.47386590286952</v>
       </c>
       <c r="K20" t="n">
         <v>57.201617928</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>4.078311652504516</v>
+        <v>9.384525841688658</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>57.201617928</v>
       </c>
       <c r="F21" t="n">
-        <v>3.997339127910541</v>
+        <v>9.589236811259996</v>
       </c>
       <c r="G21" t="n">
         <v>57.201617928</v>
       </c>
       <c r="H21" t="n">
-        <v>4.13366392993602</v>
+        <v>9.281335461196308</v>
       </c>
       <c r="I21" t="n">
         <v>57.201617928</v>
       </c>
       <c r="J21" t="n">
-        <v>3.825250940936001</v>
+        <v>9.385611345845767</v>
       </c>
       <c r="K21" t="n">
         <v>57.201617928</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.7636308704231309</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>57.201617928</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1.520147202851443</v>
       </c>
       <c r="G29" t="n">
         <v>57.201617928</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.608173360359583</v>
       </c>
       <c r="I29" t="n">
         <v>57.201617928</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1.081027399331741</v>
       </c>
       <c r="K29" t="n">
         <v>57.201617928</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.7636308704231309</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>57.201617928</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.520147202851443</v>
       </c>
       <c r="G30" t="n">
         <v>57.201617928</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.608173360359583</v>
       </c>
       <c r="I30" t="n">
         <v>57.201617928</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.081027399331741</v>
       </c>
       <c r="K30" t="n">
         <v>57.201617928</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>3.310602465359574</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>57.201617928</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>3.310602465359577</v>
       </c>
       <c r="G31" t="n">
         <v>57.201617928</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.310602465359577</v>
       </c>
       <c r="I31" t="n">
         <v>57.201617928</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>3.310602465359575</v>
       </c>
       <c r="K31" t="n">
         <v>57.201617928</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>143.6666426536025</v>
+        <v>73.00071907073274</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>73.00071907073274</v>
+        <v>143.6666426536025</v>
       </c>
     </row>
     <row r="43">
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>143.6666426536025</v>
+        <v>102.4653726520599</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>102.4653726520599</v>
+        <v>143.6666426536025</v>
       </c>
     </row>
     <row r="44">
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>143.6666426536025</v>
+        <v>116.7426165858454</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>116.7426165858454</v>
+        <v>143.6666426536025</v>
       </c>
     </row>
     <row r="45">
@@ -2103,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>143.6666426536025</v>
+        <v>124.5926448370094</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>124.5926448370094</v>
+        <v>143.6666426536025</v>
       </c>
     </row>
     <row r="46">
@@ -2137,13 +2137,13 @@
         <v>143.6666426536025</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>130.8572267136099</v>
       </c>
       <c r="G46" t="n">
-        <v>143.6666426536025</v>
+        <v>129.3263503260074</v>
       </c>
       <c r="H46" t="n">
-        <v>88.40051465185347</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>129.3263503260074</v>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>129.3263503260074</v>
+        <v>143.6666426536025</v>
       </c>
     </row>
     <row r="47">
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>47.76374028343406</v>
+        <v>41.58910293485108</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,22 +2359,22 @@
         <v>325.2478450120878</v>
       </c>
       <c r="F52" t="n">
-        <v>50.3496813137637</v>
+        <v>50.21764177109888</v>
       </c>
       <c r="G52" t="n">
-        <v>325.2478450120878</v>
+        <v>71.56181419724999</v>
       </c>
       <c r="H52" t="n">
-        <v>50.33325337847897</v>
+        <v>41.59914893927493</v>
       </c>
       <c r="I52" t="n">
         <v>71.56181419724999</v>
       </c>
       <c r="J52" t="n">
-        <v>47.31738394093405</v>
+        <v>50.20564527975104</v>
       </c>
       <c r="K52" t="n">
-        <v>71.56181419724999</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="53">
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>54.71422199721152</v>
+        <v>50.64343306816182</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,22 +2396,22 @@
         <v>325.2478450120878</v>
       </c>
       <c r="F53" t="n">
-        <v>57.96156900859886</v>
+        <v>60.03066491630418</v>
       </c>
       <c r="G53" t="n">
-        <v>325.2478450120878</v>
+        <v>116.5405528307499</v>
       </c>
       <c r="H53" t="n">
-        <v>58.07710706615381</v>
+        <v>50.68393964133163</v>
       </c>
       <c r="I53" t="n">
         <v>116.5405528307499</v>
       </c>
       <c r="J53" t="n">
-        <v>54.18097460726646</v>
+        <v>60.03066491630415</v>
       </c>
       <c r="K53" t="n">
-        <v>116.5405528307499</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="54">
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>79.24336200220007</v>
+        <v>74.95515760131774</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,22 +2433,22 @@
         <v>325.2478450120878</v>
       </c>
       <c r="F54" t="n">
-        <v>82.95136801777403</v>
+        <v>83.14269581970153</v>
       </c>
       <c r="G54" t="n">
-        <v>325.2478450120878</v>
+        <v>146.6650539247339</v>
       </c>
       <c r="H54" t="n">
-        <v>82.9074397626519</v>
+        <v>75.0056362858368</v>
       </c>
       <c r="I54" t="n">
         <v>146.6650539247339</v>
       </c>
       <c r="J54" t="n">
-        <v>78.88682348615383</v>
+        <v>83.13237559322774</v>
       </c>
       <c r="K54" t="n">
-        <v>146.6650539247339</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="55">
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>82.33642914912589</v>
+        <v>83.5374846455835</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,22 +2470,22 @@
         <v>325.2478450120878</v>
       </c>
       <c r="F55" t="n">
-        <v>81.78378375229394</v>
+        <v>79.88682348615382</v>
       </c>
       <c r="G55" t="n">
-        <v>325.2478450120878</v>
+        <v>167.9044472818541</v>
       </c>
       <c r="H55" t="n">
-        <v>81.78378375229394</v>
+        <v>83.53068322398379</v>
       </c>
       <c r="I55" t="n">
         <v>167.9044472818541</v>
       </c>
       <c r="J55" t="n">
-        <v>82.28596380489569</v>
+        <v>79.88682348615382</v>
       </c>
       <c r="K55" t="n">
-        <v>167.9044472818541</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="56">
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>82.33642914912589</v>
+        <v>83.5374846455835</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,22 +2507,22 @@
         <v>325.2478450120878</v>
       </c>
       <c r="F56" t="n">
-        <v>81.78378375229394</v>
+        <v>79.88682348615382</v>
       </c>
       <c r="G56" t="n">
-        <v>325.2478450120878</v>
+        <v>183.5048804216721</v>
       </c>
       <c r="H56" t="n">
-        <v>81.78378375229394</v>
+        <v>83.5306832239838</v>
       </c>
       <c r="I56" t="n">
         <v>183.5048804216721</v>
       </c>
       <c r="J56" t="n">
-        <v>82.28596380489569</v>
+        <v>79.88682348615383</v>
       </c>
       <c r="K56" t="n">
-        <v>183.5048804216721</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="57">
@@ -2547,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>325.2478450120878</v>
+        <v>71.56181419724999</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>71.56181419724999</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="58">
@@ -2584,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>325.2478450120878</v>
+        <v>116.5405528307499</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>116.5405528307499</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="59">
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>325.2478450120878</v>
+        <v>146.6650539247339</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>146.6650539247339</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="60">
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>325.2478450120878</v>
+        <v>167.9044472818541</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>167.9044472818541</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="61">
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>325.2478450120878</v>
+        <v>183.5048804216721</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>183.5048804216721</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="62">
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>28.06127520579207</v>
+        <v>0.05255869094350438</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>325.2478450120878</v>
       </c>
       <c r="F64" t="n">
-        <v>28.45932984065926</v>
+        <v>1.239983899681506</v>
       </c>
       <c r="G64" t="n">
         <v>325.2478450120878</v>
       </c>
       <c r="H64" t="n">
-        <v>28.45932984065923</v>
+        <v>0.3100582491410613</v>
       </c>
       <c r="I64" t="n">
         <v>325.2478450120878</v>
       </c>
       <c r="J64" t="n">
-        <v>27.76610149532954</v>
+        <v>1.459465798121049</v>
       </c>
       <c r="K64" t="n">
         <v>325.2478450120878</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>51.96934845302945</v>
+        <v>12.20176320102482</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>325.2478450120878</v>
       </c>
       <c r="F65" t="n">
-        <v>52.45932984065927</v>
+        <v>15.85523535120472</v>
       </c>
       <c r="G65" t="n">
         <v>325.2478450120878</v>
       </c>
       <c r="H65" t="n">
-        <v>52.45932984065927</v>
+        <v>12.20856462262454</v>
       </c>
       <c r="I65" t="n">
         <v>325.2478450120878</v>
       </c>
       <c r="J65" t="n">
-        <v>51.82397207393507</v>
+        <v>15.85523535120471</v>
       </c>
       <c r="K65" t="n">
         <v>325.2478450120878</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>51.96934845302945</v>
+        <v>12.20176320102482</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>325.2478450120878</v>
       </c>
       <c r="F66" t="n">
-        <v>52.45932984065927</v>
+        <v>15.85523535120472</v>
       </c>
       <c r="G66" t="n">
         <v>325.2478450120878</v>
       </c>
       <c r="H66" t="n">
-        <v>52.45932984065927</v>
+        <v>12.20856462262454</v>
       </c>
       <c r="I66" t="n">
         <v>325.2478450120878</v>
       </c>
       <c r="J66" t="n">
-        <v>51.82397207393507</v>
+        <v>15.85523535120471</v>
       </c>
       <c r="K66" t="n">
         <v>325.2478450120878</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>19.9127499941548</v>
+        <v>325.2478450120878</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>19.9127499941548</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="73">
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>35.52093422686385</v>
+        <v>325.2478450120878</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>35.52093422686385</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="74">
@@ -3182,13 +3182,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>48.23799516926555</v>
+        <v>325.2478450120878</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>48.23799516926555</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="75">
@@ -3219,13 +3219,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>58.89664954600147</v>
+        <v>325.2478450120878</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>58.89664954600147</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="76">
@@ -3256,13 +3256,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>68.00475793731587</v>
+        <v>325.2478450120878</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>68.00475793731587</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="77">
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>4.040792535109897</v>
+        <v>9.38723184814233</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3290,16 +3290,16 @@
         <v>325.2478450120878</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>9.346725274972528</v>
       </c>
       <c r="I77" t="n">
-        <v>19.9127499941548</v>
+        <v>325.2478450120878</v>
       </c>
       <c r="J77" t="n">
-        <v>4.487148877609903</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>19.9127499941548</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="78">
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>4.040792535109897</v>
+        <v>9.38723184814233</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3327,16 +3327,16 @@
         <v>325.2478450120878</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>9.346725274972528</v>
       </c>
       <c r="I78" t="n">
-        <v>35.52093422686385</v>
+        <v>325.2478450120878</v>
       </c>
       <c r="J78" t="n">
-        <v>4.487148877609903</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>35.52093422686385</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="79">
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>4.040792535109897</v>
+        <v>9.38723184814233</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3364,16 +3364,16 @@
         <v>325.2478450120878</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>9.346725274972528</v>
       </c>
       <c r="I79" t="n">
-        <v>48.23799516926555</v>
+        <v>325.2478450120878</v>
       </c>
       <c r="J79" t="n">
-        <v>4.487148877609903</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>48.23799516926555</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="80">
@@ -3404,13 +3404,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>58.89664954600147</v>
+        <v>325.2478450120878</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>58.89664954600147</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="81">
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>68.00475793731587</v>
+        <v>325.2478450120878</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>68.00475793731587</v>
+        <v>325.2478450120878</v>
       </c>
     </row>
     <row r="82">
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -3645,7 +3645,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -3680,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -3855,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -3925,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -3960,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
